--- a/www/flightdata/xlsx/eoss-338.xlsx
+++ b/www/flightdata/xlsx/eoss-338.xlsx
@@ -3588,7 +3588,7 @@
         <v>32055.82</v>
       </c>
       <c r="I2">
-        <v>613</v>
+        <v>461</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
